--- a/etf_holdings/2026-10-21_00990A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-21_00990A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-21 21:58:56</t>
+          <t>2026-10-21 22:08:03</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-21 21:58:56</t>
+          <t>2026-10-21 22:08:03</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-21 21:58:58</t>
+          <t>2026-10-21 22:08:05</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-21 21:58:58</t>
+          <t>2026-10-21 22:08:05</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-21 21:58:58</t>
+          <t>2026-10-21 22:08:05</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-21 21:58:58</t>
+          <t>2026-10-21 22:08:05</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-21 21:58:59</t>
+          <t>2026-10-21 22:08:06</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-21 21:58:59</t>
+          <t>2026-10-21 22:08:06</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-21 21:58:59</t>
+          <t>2026-10-21 22:08:06</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-21 21:58:59</t>
+          <t>2026-10-21 22:08:06</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-21 21:58:59</t>
+          <t>2026-10-21 22:08:06</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-21 21:58:59</t>
+          <t>2026-10-21 22:08:06</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
